--- a/artfynd/A 13553-2025 artfynd.xlsx
+++ b/artfynd/A 13553-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136929354</v>
       </c>
       <c r="B2" t="n">
-        <v>110333</v>
+        <v>110339</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 13553-2025 artfynd.xlsx
+++ b/artfynd/A 13553-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136929354</v>
       </c>
       <c r="B2" t="n">
-        <v>110339</v>
+        <v>110341</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 13553-2025 artfynd.xlsx
+++ b/artfynd/A 13553-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136929354</v>
       </c>
       <c r="B2" t="n">
-        <v>110341</v>
+        <v>110342</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 13553-2025 artfynd.xlsx
+++ b/artfynd/A 13553-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136929354</v>
       </c>
       <c r="B2" t="n">
-        <v>110342</v>
+        <v>110348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 13553-2025 artfynd.xlsx
+++ b/artfynd/A 13553-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136929354</v>
       </c>
       <c r="B2" t="n">
-        <v>110348</v>
+        <v>110352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 13553-2025 artfynd.xlsx
+++ b/artfynd/A 13553-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136929354</v>
       </c>
       <c r="B2" t="n">
-        <v>110352</v>
+        <v>110354</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 13553-2025 artfynd.xlsx
+++ b/artfynd/A 13553-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136929354</v>
       </c>
       <c r="B2" t="n">
-        <v>110354</v>
+        <v>110356</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 13553-2025 artfynd.xlsx
+++ b/artfynd/A 13553-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136929354</v>
       </c>
       <c r="B2" t="n">
-        <v>110356</v>
+        <v>110369</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 13553-2025 artfynd.xlsx
+++ b/artfynd/A 13553-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136929354</v>
       </c>
       <c r="B2" t="n">
-        <v>110369</v>
+        <v>110371</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 13553-2025 artfynd.xlsx
+++ b/artfynd/A 13553-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136929354</v>
       </c>
       <c r="B2" t="n">
-        <v>110371</v>
+        <v>110376</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 13553-2025 artfynd.xlsx
+++ b/artfynd/A 13553-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136929354</v>
       </c>
       <c r="B2" t="n">
-        <v>110376</v>
+        <v>110398</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 13553-2025 artfynd.xlsx
+++ b/artfynd/A 13553-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136929354</v>
       </c>
       <c r="B2" t="n">
-        <v>110398</v>
+        <v>110399</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 13553-2025 artfynd.xlsx
+++ b/artfynd/A 13553-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136929354</v>
       </c>
       <c r="B2" t="n">
-        <v>110399</v>
+        <v>110404</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 13553-2025 artfynd.xlsx
+++ b/artfynd/A 13553-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136929354</v>
       </c>
       <c r="B2" t="n">
-        <v>110404</v>
+        <v>110407</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 13553-2025 artfynd.xlsx
+++ b/artfynd/A 13553-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136929354</v>
       </c>
       <c r="B2" t="n">
-        <v>110407</v>
+        <v>110413</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 13553-2025 artfynd.xlsx
+++ b/artfynd/A 13553-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136929354</v>
       </c>
       <c r="B2" t="n">
-        <v>110413</v>
+        <v>110414</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 13553-2025 artfynd.xlsx
+++ b/artfynd/A 13553-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136929354</v>
       </c>
       <c r="B2" t="n">
-        <v>110414</v>
+        <v>110426</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 13553-2025 artfynd.xlsx
+++ b/artfynd/A 13553-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136929354</v>
       </c>
       <c r="B2" t="n">
-        <v>110426</v>
+        <v>110427</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 13553-2025 artfynd.xlsx
+++ b/artfynd/A 13553-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136929354</v>
       </c>
       <c r="B2" t="n">
-        <v>110427</v>
+        <v>110430</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 13553-2025 artfynd.xlsx
+++ b/artfynd/A 13553-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136929354</v>
       </c>
       <c r="B2" t="n">
-        <v>110430</v>
+        <v>110432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 13553-2025 artfynd.xlsx
+++ b/artfynd/A 13553-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136929354</v>
       </c>
       <c r="B2" t="n">
-        <v>110432</v>
+        <v>110436</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
